--- a/PAMaap/app/archives/XLXS_IMPORT/database.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,29 @@
         </is>
       </c>
       <c r="E3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pamapp – Manager</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pamaap2004@gmail.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$MjRFgV9gMTTRSvyM$197e0d5860a47bb6453f14640ed879c10fb0c1d7fa8a9656b4d0871f9c87df1e8cfa241ab94924914ded887b852b9e025ba22920c0ec09389f3c4e302e7229b0</t>
+        </is>
+      </c>
+      <c r="E4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -501,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +578,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pamaap2004@gmail.com</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>963018</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-03 08:16:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PAMaap/app/archives/XLXS_IMPORT/database.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/database.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +510,29 @@
         </is>
       </c>
       <c r="E4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jesus Espitia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>espitiajesusx27@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$sQ3TVEM9wS0jVEbU$68af2e8a0d4e5041d59b604717de14ce2b5173698d5cfe3736e2f42c630331f588ffe949d35d143a4b26686283bc7156ce7e0315c7c6b5d044f4c30fafb9bd93</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -524,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,6 +618,23 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>espitiajesusx27@gmail.com</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>152341</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:13:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PAMaap/app/archives/XLXS_IMPORT/database.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="2.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -470,6 +470,29 @@
         </is>
       </c>
       <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Carlos Andres Bedoya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>carlos.bedoya@arus.com.co</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$osEiuuC4DOsstiP7$5836dcfacb4e1eb42f8d64385c254344a8836601b8e2dc343b6d47d892f7eb93b354136659af2aa378717873c7fe8c4d9821b74c5db6f37da4038b08cfe45504</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -484,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="36.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -526,6 +549,23 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>carlos.bedoya@arus.com.co</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>478684</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:47:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/PAMaap/app/archives/XLXS_IMPORT/database.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/database.xlsx
@@ -1,40 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\autompython\PAMaap\app\archives\XLXS_IMPORT\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020"/>
   </bookViews>
   <sheets>
-    <sheet name="users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="codes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="users" sheetId="1" r:id="rId1"/>
+    <sheet name="codes" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>fullname</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>password_hash</t>
+  </si>
+  <si>
+    <t>verified</t>
+  </si>
+  <si>
+    <t>Jesús Manuel Espitia Guzmán</t>
+  </si>
+  <si>
+    <t>espitiaguzmanjesusmanuel@gmail.com</t>
+  </si>
+  <si>
+    <t>scrypt:32768:8:1$UGVmuu35QYAJqCQT$4231b131cf3631b1ef8ccd519446936be3160166f71986ac5cdc188eb661b98332912ab3e02c370e965c96052a34ff221dd761b04ea66b662732e93ec0fdbdd4</t>
+  </si>
+  <si>
+    <t>Carlos Andres Bedoya</t>
+  </si>
+  <si>
+    <t>carlos.bedoya@arus.com.co</t>
+  </si>
+  <si>
+    <t>scrypt:32768:8:1$osEiuuC4DOsstiP7$5836dcfacb4e1eb42f8d64385c254344a8836601b8e2dc343b6d47d892f7eb93b354136659af2aa378717873c7fe8c4d9821b74c5db6f37da4038b08cfe45504</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>expiration</t>
+  </si>
+  <si>
+    <t>624334</t>
+  </si>
+  <si>
+    <t>2026-03-10 20:06:12</t>
+  </si>
+  <si>
+    <t>478684</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:47:43</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -42,86 +110,412 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="16">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="A1:E1048576" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:E1048576"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="id" dataDxfId="5"/>
+    <tableColumn id="2" name="fullname" dataDxfId="4"/>
+    <tableColumn id="3" name="email" dataDxfId="3"/>
+    <tableColumn id="4" name="password_hash" dataDxfId="2"/>
+    <tableColumn id="5" name="verified" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:C1048576" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:C1048576"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="email" dataDxfId="12"/>
+    <tableColumn id="2" name="code" dataDxfId="11"/>
+    <tableColumn id="3" name="expiration" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,205 +802,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="2.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="28.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="36.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="168" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="168" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>password_hash</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Jesús Manuel Espitia Guzmán</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>espitiaguzmanjesusmanuel@gmail.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$UGVmuu35QYAJqCQT$4231b131cf3631b1ef8ccd519446936be3160166f71986ac5cdc188eb661b98332912ab3e02c370e965c96052a34ff221dd761b04ea66b662732e93ec0fdbdd4</t>
-        </is>
-      </c>
-      <c r="E2" t="b">
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Carlos Andres Bedoya</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>carlos.bedoya@arus.com.co</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$osEiuuC4DOsstiP7$5836dcfacb4e1eb42f8d64385c254344a8836601b8e2dc343b6d47d892f7eb93b354136659af2aa378717873c7fe8c4d9821b74c5db6f37da4038b08cfe45504</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>manuel guzman</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>jesuselcandy@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$23oiODuSFYT7jSGu$de30a15955607108e2b43049b3f6e022eedccde897288fac6a264d9264972702dd73feabbe6059f7c5abf66b158e414cd399e67bc1b481cd28f1269dfa2eab5d</t>
-        </is>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
+    <row r="1048576" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1048576" s="7"/>
+      <c r="B1048576" s="8"/>
+      <c r="C1048576" s="8"/>
+      <c r="D1048576" s="8"/>
+      <c r="E1048576" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C1048576"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="36.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="7" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="18.140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>expiration</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>espitiaguzmanjesusmanuel@gmail.com</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>624334</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-03-10 20:06:12</t>
-        </is>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>carlos.bedoya@arus.com.co</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>478684</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-03-11 12:47:43</t>
-        </is>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>jesuselcandy@gmail.com</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>132361</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-03-24 14:39:37</t>
-        </is>
-      </c>
+    <row r="1048576" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1048576" s="7"/>
+      <c r="B1048576" s="8"/>
+      <c r="C1048576" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>